--- a/AAII_Financials/Quarterly/CBDBY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/CBDBY_QTR_FIN.xlsx
@@ -305,7 +305,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="1">
-    <numFmt numFmtId="165" formatCode="[$-409]d\-mmm\-yy;@"/>
+    <numFmt numFmtId="164" formatCode="[$-409]d\-mmm\-yy;@"/>
   </numFmts>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
@@ -347,7 +347,7 @@
   <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -715,25 +715,25 @@
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>847300</v>
+        <v>824200</v>
       </c>
       <c r="E8" s="3">
-        <v>971300</v>
+        <v>944800</v>
       </c>
       <c r="F8" s="3">
-        <v>876100</v>
+        <v>852300</v>
       </c>
       <c r="G8" s="3">
-        <v>878500</v>
+        <v>854600</v>
       </c>
       <c r="H8" s="3">
-        <v>768000</v>
+        <v>747100</v>
       </c>
       <c r="I8" s="3">
-        <v>3200200</v>
+        <v>3113100</v>
       </c>
       <c r="J8" s="3">
-        <v>798500</v>
+        <v>776800</v>
       </c>
       <c r="K8" s="3">
         <v>773800</v>
@@ -744,25 +744,25 @@
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>617300</v>
+        <v>600500</v>
       </c>
       <c r="E9" s="3">
-        <v>722200</v>
+        <v>702600</v>
       </c>
       <c r="F9" s="3">
-        <v>656100</v>
+        <v>638200</v>
       </c>
       <c r="G9" s="3">
-        <v>660100</v>
+        <v>642200</v>
       </c>
       <c r="H9" s="3">
-        <v>570700</v>
+        <v>555200</v>
       </c>
       <c r="I9" s="3">
-        <v>2405400</v>
+        <v>2339900</v>
       </c>
       <c r="J9" s="3">
-        <v>608800</v>
+        <v>592200</v>
       </c>
       <c r="K9" s="3">
         <v>567800</v>
@@ -773,25 +773,25 @@
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>230000</v>
+        <v>223800</v>
       </c>
       <c r="E10" s="3">
-        <v>249100</v>
+        <v>242300</v>
       </c>
       <c r="F10" s="3">
-        <v>220000</v>
+        <v>214100</v>
       </c>
       <c r="G10" s="3">
-        <v>218400</v>
+        <v>212400</v>
       </c>
       <c r="H10" s="3">
-        <v>197300</v>
+        <v>192000</v>
       </c>
       <c r="I10" s="3">
-        <v>794800</v>
+        <v>773200</v>
       </c>
       <c r="J10" s="3">
-        <v>189700</v>
+        <v>184600</v>
       </c>
       <c r="K10" s="3">
         <v>206000</v>
@@ -873,25 +873,25 @@
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>8300</v>
+        <v>8100</v>
       </c>
       <c r="E14" s="3">
-        <v>34200</v>
+        <v>33300</v>
       </c>
       <c r="F14" s="3">
-        <v>17900</v>
+        <v>17400</v>
       </c>
       <c r="G14" s="3">
-        <v>12600</v>
+        <v>12200</v>
       </c>
       <c r="H14" s="3">
-        <v>4800</v>
+        <v>4700</v>
       </c>
       <c r="I14" s="3">
-        <v>58200</v>
+        <v>56600</v>
       </c>
       <c r="J14" s="3">
-        <v>12400</v>
+        <v>12000</v>
       </c>
       <c r="K14" s="3">
         <v>5400</v>
@@ -902,25 +902,25 @@
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>47300</v>
+        <v>46000</v>
       </c>
       <c r="E15" s="3">
-        <v>47500</v>
+        <v>46200</v>
       </c>
       <c r="F15" s="3">
-        <v>47300</v>
+        <v>46000</v>
       </c>
       <c r="G15" s="3">
-        <v>46900</v>
+        <v>45700</v>
       </c>
       <c r="H15" s="3">
-        <v>45600</v>
+        <v>44400</v>
       </c>
       <c r="I15" s="3">
-        <v>172000</v>
+        <v>167300</v>
       </c>
       <c r="J15" s="3">
-        <v>45100</v>
+        <v>43900</v>
       </c>
       <c r="K15" s="3">
         <v>40300</v>
@@ -941,25 +941,25 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>869300</v>
+        <v>845600</v>
       </c>
       <c r="E17" s="3">
-        <v>965700</v>
+        <v>939400</v>
       </c>
       <c r="F17" s="3">
-        <v>727800</v>
+        <v>708000</v>
       </c>
       <c r="G17" s="3">
-        <v>888000</v>
+        <v>863800</v>
       </c>
       <c r="H17" s="3">
-        <v>788400</v>
+        <v>766900</v>
       </c>
       <c r="I17" s="3">
-        <v>3304600</v>
+        <v>3214700</v>
       </c>
       <c r="J17" s="3">
-        <v>821100</v>
+        <v>798700</v>
       </c>
       <c r="K17" s="3">
         <v>783600</v>
@@ -970,25 +970,25 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>-22000</v>
+        <v>-21400</v>
       </c>
       <c r="E18" s="3">
-        <v>5500</v>
+        <v>5400</v>
       </c>
       <c r="F18" s="3">
-        <v>148400</v>
+        <v>144300</v>
       </c>
       <c r="G18" s="3">
-        <v>-9400</v>
+        <v>-9200</v>
       </c>
       <c r="H18" s="3">
-        <v>-20300</v>
+        <v>-19800</v>
       </c>
       <c r="I18" s="3">
-        <v>-104400</v>
+        <v>-101500</v>
       </c>
       <c r="J18" s="3">
-        <v>-22500</v>
+        <v>-21900</v>
       </c>
       <c r="K18" s="3">
         <v>-9800</v>
@@ -1015,10 +1015,10 @@
         <v>-2000</v>
       </c>
       <c r="E20" s="3">
-        <v>24000</v>
+        <v>23400</v>
       </c>
       <c r="F20" s="3">
-        <v>30900</v>
+        <v>30000</v>
       </c>
       <c r="G20" s="3">
         <v>-400</v>
@@ -1027,10 +1027,10 @@
         <v>400</v>
       </c>
       <c r="I20" s="3">
-        <v>93500</v>
+        <v>90900</v>
       </c>
       <c r="J20" s="3">
-        <v>29700</v>
+        <v>28900</v>
       </c>
       <c r="K20" s="3">
         <v>11300</v>
@@ -1041,25 +1041,25 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>29000</v>
+        <v>28200</v>
       </c>
       <c r="E21" s="3">
-        <v>82400</v>
+        <v>80200</v>
       </c>
       <c r="F21" s="3">
-        <v>231900</v>
+        <v>225600</v>
       </c>
       <c r="G21" s="3">
-        <v>42900</v>
+        <v>41700</v>
       </c>
       <c r="H21" s="3">
-        <v>31800</v>
+        <v>30900</v>
       </c>
       <c r="I21" s="3">
-        <v>340500</v>
+        <v>331200</v>
       </c>
       <c r="J21" s="3">
-        <v>95500</v>
+        <v>92900</v>
       </c>
       <c r="K21" s="3">
         <v>88300</v>
@@ -1070,25 +1070,25 @@
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>52800</v>
+        <v>51400</v>
       </c>
       <c r="E22" s="3">
-        <v>55200</v>
+        <v>53700</v>
       </c>
       <c r="F22" s="3">
-        <v>62300</v>
+        <v>60600</v>
       </c>
       <c r="G22" s="3">
-        <v>62100</v>
+        <v>60400</v>
       </c>
       <c r="H22" s="3">
-        <v>61500</v>
+        <v>59900</v>
       </c>
       <c r="I22" s="3">
-        <v>232100</v>
+        <v>225700</v>
       </c>
       <c r="J22" s="3">
-        <v>64300</v>
+        <v>62500</v>
       </c>
       <c r="K22" s="3">
         <v>58200</v>
@@ -1099,25 +1099,25 @@
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>-76900</v>
+        <v>-74800</v>
       </c>
       <c r="E23" s="3">
-        <v>-25700</v>
+        <v>-25000</v>
       </c>
       <c r="F23" s="3">
-        <v>117000</v>
+        <v>113800</v>
       </c>
       <c r="G23" s="3">
-        <v>-71900</v>
+        <v>-69900</v>
       </c>
       <c r="H23" s="3">
-        <v>-81500</v>
+        <v>-79300</v>
       </c>
       <c r="I23" s="3">
-        <v>-243000</v>
+        <v>-236300</v>
       </c>
       <c r="J23" s="3">
-        <v>-57100</v>
+        <v>-55500</v>
       </c>
       <c r="K23" s="3">
         <v>-56700</v>
@@ -1131,22 +1131,22 @@
         <v>-1800</v>
       </c>
       <c r="E24" s="3">
-        <v>-9800</v>
+        <v>-9500</v>
       </c>
       <c r="F24" s="3">
-        <v>-32300</v>
+        <v>-31500</v>
       </c>
       <c r="G24" s="3">
-        <v>-12600</v>
+        <v>-12200</v>
       </c>
       <c r="H24" s="3">
-        <v>-22500</v>
+        <v>-21900</v>
       </c>
       <c r="I24" s="3">
-        <v>-83900</v>
+        <v>-81600</v>
       </c>
       <c r="J24" s="3">
-        <v>-15000</v>
+        <v>-14600</v>
       </c>
       <c r="K24" s="3">
         <v>-17600</v>
@@ -1186,25 +1186,25 @@
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>-75000</v>
+        <v>-73000</v>
       </c>
       <c r="E26" s="3">
-        <v>-15900</v>
+        <v>-15500</v>
       </c>
       <c r="F26" s="3">
-        <v>149300</v>
+        <v>145200</v>
       </c>
       <c r="G26" s="3">
-        <v>-59300</v>
+        <v>-57700</v>
       </c>
       <c r="H26" s="3">
-        <v>-58900</v>
+        <v>-57300</v>
       </c>
       <c r="I26" s="3">
-        <v>-159100</v>
+        <v>-154700</v>
       </c>
       <c r="J26" s="3">
-        <v>-42100</v>
+        <v>-41000</v>
       </c>
       <c r="K26" s="3">
         <v>-39200</v>
@@ -1215,25 +1215,25 @@
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>-75200</v>
+        <v>-73200</v>
       </c>
       <c r="E27" s="3">
-        <v>-16300</v>
+        <v>-15800</v>
       </c>
       <c r="F27" s="3">
-        <v>147600</v>
+        <v>143600</v>
       </c>
       <c r="G27" s="3">
-        <v>-72800</v>
+        <v>-70800</v>
       </c>
       <c r="H27" s="3">
-        <v>-68700</v>
+        <v>-66900</v>
       </c>
       <c r="I27" s="3">
-        <v>-190100</v>
+        <v>-184900</v>
       </c>
       <c r="J27" s="3">
-        <v>-51700</v>
+        <v>-50300</v>
       </c>
       <c r="K27" s="3">
         <v>-48200</v>
@@ -1273,25 +1273,25 @@
         <v>24</v>
       </c>
       <c r="D29" s="3">
-        <v>-46700</v>
+        <v>-45500</v>
       </c>
       <c r="E29" s="3">
-        <v>-39700</v>
+        <v>-38600</v>
       </c>
       <c r="F29" s="3">
-        <v>-386900</v>
+        <v>-376400</v>
       </c>
       <c r="G29" s="3">
-        <v>-5700</v>
+        <v>-5600</v>
       </c>
       <c r="H29" s="3">
-        <v>22900</v>
+        <v>22300</v>
       </c>
       <c r="I29" s="3">
-        <v>158300</v>
+        <v>154000</v>
       </c>
       <c r="J29" s="3">
-        <v>-3000</v>
+        <v>-2900</v>
       </c>
       <c r="K29" s="3">
         <v>16300</v>
@@ -1363,10 +1363,10 @@
         <v>2000</v>
       </c>
       <c r="E32" s="3">
-        <v>-24000</v>
+        <v>-23400</v>
       </c>
       <c r="F32" s="3">
-        <v>-30900</v>
+        <v>-30000</v>
       </c>
       <c r="G32" s="3">
         <v>400</v>
@@ -1375,10 +1375,10 @@
         <v>-400</v>
       </c>
       <c r="I32" s="3">
-        <v>-93500</v>
+        <v>-90900</v>
       </c>
       <c r="J32" s="3">
-        <v>-29700</v>
+        <v>-28900</v>
       </c>
       <c r="K32" s="3">
         <v>-11300</v>
@@ -1389,25 +1389,25 @@
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>-121900</v>
+        <v>-118600</v>
       </c>
       <c r="E33" s="3">
-        <v>-56000</v>
+        <v>-54500</v>
       </c>
       <c r="F33" s="3">
-        <v>-239300</v>
+        <v>-232800</v>
       </c>
       <c r="G33" s="3">
-        <v>-78500</v>
+        <v>-76400</v>
       </c>
       <c r="H33" s="3">
-        <v>-45800</v>
+        <v>-44600</v>
       </c>
       <c r="I33" s="3">
-        <v>-31800</v>
+        <v>-30900</v>
       </c>
       <c r="J33" s="3">
-        <v>-54700</v>
+        <v>-53200</v>
       </c>
       <c r="K33" s="3">
         <v>-32000</v>
@@ -1447,25 +1447,25 @@
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>-121900</v>
+        <v>-118600</v>
       </c>
       <c r="E35" s="3">
-        <v>-56000</v>
+        <v>-54500</v>
       </c>
       <c r="F35" s="3">
-        <v>-239300</v>
+        <v>-232800</v>
       </c>
       <c r="G35" s="3">
-        <v>-78500</v>
+        <v>-76400</v>
       </c>
       <c r="H35" s="3">
-        <v>-45800</v>
+        <v>-44600</v>
       </c>
       <c r="I35" s="3">
-        <v>-31800</v>
+        <v>-30900</v>
       </c>
       <c r="J35" s="3">
-        <v>-54700</v>
+        <v>-53200</v>
       </c>
       <c r="K35" s="3">
         <v>-32000</v>
@@ -1536,25 +1536,25 @@
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>523200</v>
+        <v>509000</v>
       </c>
       <c r="E41" s="3">
-        <v>548900</v>
+        <v>534000</v>
       </c>
       <c r="F41" s="3">
-        <v>559600</v>
+        <v>544400</v>
       </c>
       <c r="G41" s="3">
-        <v>594400</v>
+        <v>578200</v>
       </c>
       <c r="H41" s="3">
-        <v>649600</v>
+        <v>631900</v>
       </c>
       <c r="I41" s="3">
-        <v>693000</v>
+        <v>674200</v>
       </c>
       <c r="J41" s="3">
-        <v>713200</v>
+        <v>693800</v>
       </c>
       <c r="K41" s="3">
         <v>723900</v>
@@ -1568,10 +1568,10 @@
         <v>3100</v>
       </c>
       <c r="E42" s="3">
-        <v>143600</v>
+        <v>139700</v>
       </c>
       <c r="F42" s="3">
-        <v>131400</v>
+        <v>127800</v>
       </c>
       <c r="G42" s="3" t="s">
         <v>8</v>
@@ -1594,25 +1594,25 @@
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>204000</v>
+        <v>198400</v>
       </c>
       <c r="E43" s="3">
-        <v>305000</v>
+        <v>296700</v>
       </c>
       <c r="F43" s="3">
-        <v>374900</v>
+        <v>364700</v>
       </c>
       <c r="G43" s="3">
-        <v>315900</v>
+        <v>307300</v>
       </c>
       <c r="H43" s="3">
-        <v>305400</v>
+        <v>297100</v>
       </c>
       <c r="I43" s="3">
-        <v>334400</v>
+        <v>325300</v>
       </c>
       <c r="J43" s="3">
-        <v>756400</v>
+        <v>735800</v>
       </c>
       <c r="K43" s="3">
         <v>1031500</v>
@@ -1623,25 +1623,25 @@
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>347900</v>
+        <v>338400</v>
       </c>
       <c r="E44" s="3">
-        <v>360700</v>
+        <v>350800</v>
       </c>
       <c r="F44" s="3">
-        <v>368000</v>
+        <v>358000</v>
       </c>
       <c r="G44" s="3">
-        <v>363100</v>
+        <v>353200</v>
       </c>
       <c r="H44" s="3">
-        <v>384100</v>
+        <v>373700</v>
       </c>
       <c r="I44" s="3">
-        <v>378000</v>
+        <v>367700</v>
       </c>
       <c r="J44" s="3">
-        <v>1023400</v>
+        <v>995500</v>
       </c>
       <c r="K44" s="3">
         <v>987700</v>
@@ -1652,25 +1652,25 @@
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>109400</v>
+        <v>106400</v>
       </c>
       <c r="E45" s="3">
-        <v>31800</v>
+        <v>30900</v>
       </c>
       <c r="F45" s="3">
-        <v>32300</v>
+        <v>31500</v>
       </c>
       <c r="G45" s="3">
-        <v>4075600</v>
+        <v>3964700</v>
       </c>
       <c r="H45" s="3">
-        <v>3831400</v>
+        <v>3727100</v>
       </c>
       <c r="I45" s="3">
-        <v>3871100</v>
+        <v>3765700</v>
       </c>
       <c r="J45" s="3">
-        <v>65000</v>
+        <v>63300</v>
       </c>
       <c r="K45" s="3">
         <v>100700</v>
@@ -1681,25 +1681,25 @@
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>1187600</v>
+        <v>1155300</v>
       </c>
       <c r="E46" s="3">
-        <v>1389900</v>
+        <v>1352100</v>
       </c>
       <c r="F46" s="3">
-        <v>1466300</v>
+        <v>1426300</v>
       </c>
       <c r="G46" s="3">
-        <v>5349000</v>
+        <v>5203400</v>
       </c>
       <c r="H46" s="3">
-        <v>5170500</v>
+        <v>5029700</v>
       </c>
       <c r="I46" s="3">
-        <v>5276600</v>
+        <v>5132900</v>
       </c>
       <c r="J46" s="3">
-        <v>2558000</v>
+        <v>2488400</v>
       </c>
       <c r="K46" s="3">
         <v>2843800</v>
@@ -1710,25 +1710,25 @@
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>838100</v>
+        <v>815300</v>
       </c>
       <c r="E47" s="3">
-        <v>787400</v>
+        <v>766000</v>
       </c>
       <c r="F47" s="3">
-        <v>789100</v>
+        <v>767600</v>
       </c>
       <c r="G47" s="3">
-        <v>857100</v>
+        <v>833800</v>
       </c>
       <c r="H47" s="3">
-        <v>852900</v>
+        <v>829600</v>
       </c>
       <c r="I47" s="3">
-        <v>862600</v>
+        <v>839200</v>
       </c>
       <c r="J47" s="3">
-        <v>835700</v>
+        <v>812900</v>
       </c>
       <c r="K47" s="3">
         <v>946900</v>
@@ -1739,25 +1739,25 @@
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>1155900</v>
+        <v>1124400</v>
       </c>
       <c r="E48" s="3">
-        <v>1215200</v>
+        <v>1182100</v>
       </c>
       <c r="F48" s="3">
-        <v>1191700</v>
+        <v>1159300</v>
       </c>
       <c r="G48" s="3">
-        <v>1245500</v>
+        <v>1211600</v>
       </c>
       <c r="H48" s="3">
-        <v>1275800</v>
+        <v>1241000</v>
       </c>
       <c r="I48" s="3">
-        <v>1264500</v>
+        <v>1230100</v>
       </c>
       <c r="J48" s="3">
-        <v>3368900</v>
+        <v>3277200</v>
       </c>
       <c r="K48" s="3">
         <v>3444900</v>
@@ -1768,25 +1768,25 @@
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>360100</v>
+        <v>350300</v>
       </c>
       <c r="E49" s="3">
-        <v>364500</v>
+        <v>354600</v>
       </c>
       <c r="F49" s="3">
-        <v>357000</v>
+        <v>347200</v>
       </c>
       <c r="G49" s="3">
-        <v>368400</v>
+        <v>358400</v>
       </c>
       <c r="H49" s="3">
-        <v>370100</v>
+        <v>360000</v>
       </c>
       <c r="I49" s="3">
-        <v>366900</v>
+        <v>356900</v>
       </c>
       <c r="J49" s="3">
-        <v>970000</v>
+        <v>943600</v>
       </c>
       <c r="K49" s="3">
         <v>1009200</v>
@@ -1855,25 +1855,25 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>312800</v>
+        <v>304300</v>
       </c>
       <c r="E52" s="3">
-        <v>316900</v>
+        <v>308200</v>
       </c>
       <c r="F52" s="3">
-        <v>387300</v>
+        <v>376700</v>
       </c>
       <c r="G52" s="3">
-        <v>383000</v>
+        <v>372600</v>
       </c>
       <c r="H52" s="3">
-        <v>359400</v>
+        <v>349600</v>
       </c>
       <c r="I52" s="3">
-        <v>329100</v>
+        <v>320100</v>
       </c>
       <c r="J52" s="3">
-        <v>284300</v>
+        <v>276600</v>
       </c>
       <c r="K52" s="3">
         <v>264600</v>
@@ -1913,25 +1913,25 @@
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>3854500</v>
+        <v>3749500</v>
       </c>
       <c r="E54" s="3">
-        <v>4074000</v>
+        <v>3963000</v>
       </c>
       <c r="F54" s="3">
-        <v>4191300</v>
+        <v>4077200</v>
       </c>
       <c r="G54" s="3">
-        <v>8203000</v>
+        <v>7979700</v>
       </c>
       <c r="H54" s="3">
-        <v>8028600</v>
+        <v>7810000</v>
       </c>
       <c r="I54" s="3">
-        <v>8099700</v>
+        <v>7879200</v>
       </c>
       <c r="J54" s="3">
-        <v>8016900</v>
+        <v>7798700</v>
       </c>
       <c r="K54" s="3">
         <v>8509300</v>
@@ -1968,25 +1968,25 @@
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>462800</v>
+        <v>450200</v>
       </c>
       <c r="E57" s="3">
-        <v>601000</v>
+        <v>584700</v>
       </c>
       <c r="F57" s="3">
-        <v>455600</v>
+        <v>443200</v>
       </c>
       <c r="G57" s="3">
-        <v>462800</v>
+        <v>450200</v>
       </c>
       <c r="H57" s="3">
-        <v>452800</v>
+        <v>440500</v>
       </c>
       <c r="I57" s="3">
-        <v>577000</v>
+        <v>561300</v>
       </c>
       <c r="J57" s="3">
-        <v>1233600</v>
+        <v>1200100</v>
       </c>
       <c r="K57" s="3">
         <v>1311800</v>
@@ -1997,25 +1997,25 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>270900</v>
+        <v>263500</v>
       </c>
       <c r="E58" s="3">
-        <v>267200</v>
+        <v>259900</v>
       </c>
       <c r="F58" s="3">
-        <v>353600</v>
+        <v>344000</v>
       </c>
       <c r="G58" s="3">
-        <v>386500</v>
+        <v>376000</v>
       </c>
       <c r="H58" s="3">
-        <v>299500</v>
+        <v>291300</v>
       </c>
       <c r="I58" s="3">
-        <v>275500</v>
+        <v>268000</v>
       </c>
       <c r="J58" s="3">
-        <v>564300</v>
+        <v>548900</v>
       </c>
       <c r="K58" s="3">
         <v>682300</v>
@@ -2026,25 +2026,25 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>331100</v>
+        <v>322100</v>
       </c>
       <c r="E59" s="3">
-        <v>281900</v>
+        <v>274300</v>
       </c>
       <c r="F59" s="3">
-        <v>305200</v>
+        <v>296900</v>
       </c>
       <c r="G59" s="3">
-        <v>2502200</v>
+        <v>2434100</v>
       </c>
       <c r="H59" s="3">
-        <v>2335900</v>
+        <v>2272300</v>
       </c>
       <c r="I59" s="3">
-        <v>2426500</v>
+        <v>2360400</v>
       </c>
       <c r="J59" s="3">
-        <v>597300</v>
+        <v>581100</v>
       </c>
       <c r="K59" s="3">
         <v>695400</v>
@@ -2055,25 +2055,25 @@
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>1064800</v>
+        <v>1035800</v>
       </c>
       <c r="E60" s="3">
-        <v>1150100</v>
+        <v>1118800</v>
       </c>
       <c r="F60" s="3">
-        <v>1114500</v>
+        <v>1084100</v>
       </c>
       <c r="G60" s="3">
-        <v>3351500</v>
+        <v>3260300</v>
       </c>
       <c r="H60" s="3">
-        <v>3088300</v>
+        <v>3004200</v>
       </c>
       <c r="I60" s="3">
-        <v>3278900</v>
+        <v>3189700</v>
       </c>
       <c r="J60" s="3">
-        <v>2395200</v>
+        <v>2330000</v>
       </c>
       <c r="K60" s="3">
         <v>2689600</v>
@@ -2084,25 +2084,25 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>1368700</v>
+        <v>1331400</v>
       </c>
       <c r="E61" s="3">
-        <v>1501700</v>
+        <v>1460800</v>
       </c>
       <c r="F61" s="3">
-        <v>1516900</v>
+        <v>1475600</v>
       </c>
       <c r="G61" s="3">
-        <v>1523900</v>
+        <v>1482400</v>
       </c>
       <c r="H61" s="3">
-        <v>1661200</v>
+        <v>1616000</v>
       </c>
       <c r="I61" s="3">
-        <v>1553600</v>
+        <v>1511300</v>
       </c>
       <c r="J61" s="3">
-        <v>1971600</v>
+        <v>1917900</v>
       </c>
       <c r="K61" s="3">
         <v>1998500</v>
@@ -2113,25 +2113,25 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>558900</v>
+        <v>543700</v>
       </c>
       <c r="E62" s="3">
-        <v>549700</v>
+        <v>534700</v>
       </c>
       <c r="F62" s="3">
-        <v>632600</v>
+        <v>615400</v>
       </c>
       <c r="G62" s="3">
-        <v>792800</v>
+        <v>771200</v>
       </c>
       <c r="H62" s="3">
-        <v>754000</v>
+        <v>733500</v>
       </c>
       <c r="I62" s="3">
-        <v>729800</v>
+        <v>709900</v>
       </c>
       <c r="J62" s="3">
-        <v>710600</v>
+        <v>691200</v>
       </c>
       <c r="K62" s="3">
         <v>720400</v>
@@ -2229,25 +2229,25 @@
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>2993300</v>
+        <v>2911800</v>
       </c>
       <c r="E66" s="3">
-        <v>3202100</v>
+        <v>3114900</v>
       </c>
       <c r="F66" s="3">
-        <v>3264300</v>
+        <v>3175500</v>
       </c>
       <c r="G66" s="3">
-        <v>5818500</v>
+        <v>5660100</v>
       </c>
       <c r="H66" s="3">
-        <v>5574900</v>
+        <v>5423200</v>
       </c>
       <c r="I66" s="3">
-        <v>5966600</v>
+        <v>5804200</v>
       </c>
       <c r="J66" s="3">
-        <v>5515500</v>
+        <v>5365300</v>
       </c>
       <c r="K66" s="3">
         <v>5873000</v>
@@ -2387,25 +2387,25 @@
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>69300</v>
+        <v>67400</v>
       </c>
       <c r="E72" s="3">
-        <v>210100</v>
+        <v>204400</v>
       </c>
       <c r="F72" s="3">
-        <v>265100</v>
+        <v>257900</v>
       </c>
       <c r="G72" s="3">
-        <v>503100</v>
+        <v>489400</v>
       </c>
       <c r="H72" s="3">
-        <v>580700</v>
+        <v>564900</v>
       </c>
       <c r="I72" s="3">
-        <v>1107100</v>
+        <v>1076900</v>
       </c>
       <c r="J72" s="3">
-        <v>1308800</v>
+        <v>1273200</v>
       </c>
       <c r="K72" s="3">
         <v>1334700</v>
@@ -2503,25 +2503,25 @@
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>861200</v>
+        <v>837700</v>
       </c>
       <c r="E76" s="3">
-        <v>871900</v>
+        <v>848100</v>
       </c>
       <c r="F76" s="3">
-        <v>926900</v>
+        <v>901700</v>
       </c>
       <c r="G76" s="3">
-        <v>2384500</v>
+        <v>2319600</v>
       </c>
       <c r="H76" s="3">
-        <v>2453600</v>
+        <v>2386800</v>
       </c>
       <c r="I76" s="3">
-        <v>2133100</v>
+        <v>2075000</v>
       </c>
       <c r="J76" s="3">
-        <v>2501500</v>
+        <v>2433400</v>
       </c>
       <c r="K76" s="3">
         <v>2636300</v>
@@ -2595,25 +2595,25 @@
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>-121900</v>
+        <v>-118600</v>
       </c>
       <c r="E81" s="3">
-        <v>-56000</v>
+        <v>-54500</v>
       </c>
       <c r="F81" s="3">
-        <v>-239300</v>
+        <v>-232800</v>
       </c>
       <c r="G81" s="3">
-        <v>-78500</v>
+        <v>-76400</v>
       </c>
       <c r="H81" s="3">
-        <v>-45800</v>
+        <v>-44600</v>
       </c>
       <c r="I81" s="3">
-        <v>-31800</v>
+        <v>-30900</v>
       </c>
       <c r="J81" s="3">
-        <v>-54700</v>
+        <v>-53200</v>
       </c>
       <c r="K81" s="3">
         <v>-32000</v>
@@ -2637,25 +2637,25 @@
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>53000</v>
+        <v>51600</v>
       </c>
       <c r="E83" s="3">
-        <v>52800</v>
+        <v>51400</v>
       </c>
       <c r="F83" s="3">
-        <v>52700</v>
+        <v>51200</v>
       </c>
       <c r="G83" s="3">
-        <v>52700</v>
+        <v>51200</v>
       </c>
       <c r="H83" s="3">
-        <v>51700</v>
+        <v>50300</v>
       </c>
       <c r="I83" s="3">
-        <v>351400</v>
+        <v>341800</v>
       </c>
       <c r="J83" s="3">
-        <v>88300</v>
+        <v>85900</v>
       </c>
       <c r="K83" s="3">
         <v>86800</v>
@@ -2811,25 +2811,25 @@
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>-54300</v>
+        <v>-52800</v>
       </c>
       <c r="E89" s="3">
-        <v>214700</v>
+        <v>208800</v>
       </c>
       <c r="F89" s="3">
-        <v>-21200</v>
+        <v>-20700</v>
       </c>
       <c r="G89" s="3">
-        <v>174600</v>
+        <v>169800</v>
       </c>
       <c r="H89" s="3">
-        <v>-264000</v>
+        <v>-256800</v>
       </c>
       <c r="I89" s="3">
-        <v>-39900</v>
+        <v>-38800</v>
       </c>
       <c r="J89" s="3">
-        <v>-34600</v>
+        <v>-33600</v>
       </c>
       <c r="K89" s="3">
         <v>145600</v>
@@ -2940,25 +2940,25 @@
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>111400</v>
+        <v>108400</v>
       </c>
       <c r="E94" s="3">
-        <v>-17900</v>
+        <v>-17400</v>
       </c>
       <c r="F94" s="3">
-        <v>-195700</v>
+        <v>-190300</v>
       </c>
       <c r="G94" s="3">
         <v>-2000</v>
       </c>
       <c r="H94" s="3">
-        <v>-79400</v>
+        <v>-77300</v>
       </c>
       <c r="I94" s="3">
-        <v>523600</v>
+        <v>509400</v>
       </c>
       <c r="J94" s="3">
-        <v>255000</v>
+        <v>248000</v>
       </c>
       <c r="K94" s="3">
         <v>27700</v>
@@ -2988,19 +2988,19 @@
         <v>0</v>
       </c>
       <c r="F96" s="3">
-        <v>-5200</v>
+        <v>-5000</v>
       </c>
       <c r="G96" s="3">
-        <v>-10300</v>
+        <v>-10100</v>
       </c>
       <c r="H96" s="3">
-        <v>-5200</v>
+        <v>-5000</v>
       </c>
       <c r="I96" s="3">
-        <v>-49000</v>
+        <v>-47600</v>
       </c>
       <c r="J96" s="3">
-        <v>-2600</v>
+        <v>-2500</v>
       </c>
       <c r="K96" s="3">
         <v>-25500</v>
@@ -3098,25 +3098,25 @@
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>-82800</v>
+        <v>-80500</v>
       </c>
       <c r="E100" s="3">
-        <v>-207300</v>
+        <v>-201700</v>
       </c>
       <c r="F100" s="3">
-        <v>-121000</v>
+        <v>-117700</v>
       </c>
       <c r="G100" s="3">
-        <v>-138600</v>
+        <v>-134800</v>
       </c>
       <c r="H100" s="3">
-        <v>151900</v>
+        <v>147700</v>
       </c>
       <c r="I100" s="3">
-        <v>-868900</v>
+        <v>-845300</v>
       </c>
       <c r="J100" s="3">
-        <v>-206900</v>
+        <v>-201300</v>
       </c>
       <c r="K100" s="3">
         <v>-113400</v>
@@ -3133,19 +3133,19 @@
         <v>0</v>
       </c>
       <c r="F101" s="3">
-        <v>4800</v>
+        <v>4700</v>
       </c>
       <c r="G101" s="3">
-        <v>9600</v>
+        <v>9300</v>
       </c>
       <c r="H101" s="3">
         <v>2000</v>
       </c>
       <c r="I101" s="3">
-        <v>-104900</v>
+        <v>-102100</v>
       </c>
       <c r="J101" s="3">
-        <v>-24200</v>
+        <v>-23500</v>
       </c>
       <c r="K101" s="3">
         <v>-3000</v>
@@ -3156,25 +3156,25 @@
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>-25700</v>
+        <v>-25000</v>
       </c>
       <c r="E102" s="3">
-        <v>-10500</v>
+        <v>-10200</v>
       </c>
       <c r="F102" s="3">
-        <v>-333100</v>
+        <v>-324100</v>
       </c>
       <c r="G102" s="3">
-        <v>43600</v>
+        <v>42400</v>
       </c>
       <c r="H102" s="3">
-        <v>-189600</v>
+        <v>-184400</v>
       </c>
       <c r="I102" s="3">
-        <v>-490200</v>
+        <v>-476800</v>
       </c>
       <c r="J102" s="3">
-        <v>-10700</v>
+        <v>-10400</v>
       </c>
       <c r="K102" s="3">
         <v>56900</v>
